--- a/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,18 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -845,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -875,6 +887,98 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920377</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920377</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920378</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920378</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,18 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
   </si>
 </sst>
 </file>
@@ -626,16 +614,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -649,16 +640,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -672,16 +666,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -695,16 +692,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -769,7 +769,7 @@
         <v>95.45</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,7 +795,7 @@
         <v>95.45</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -812,16 +812,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -838,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -857,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -887,98 +887,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920377</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920377</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920378</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920378</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20212.xlsx
@@ -760,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -786,16 +786,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -812,16 +812,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -838,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>78.79000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
